--- a/wbs-assessment/260803_LAICA_WBS_RevOps_Assessment_V.1.1.xlsx
+++ b/wbs-assessment/260803_LAICA_WBS_RevOps_Assessment_V.1.1.xlsx
@@ -10,9 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametri" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ruoli" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametri" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ruoli" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$2:$AA$13</definedName>
@@ -4395,19 +4394,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
@@ -4781,7 +4767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
